--- a/backend/data/financials_by_company/000875.SZ.xlsx
+++ b/backend/data/financials_by_company/000875.SZ.xlsx
@@ -4044,207 +4044,207 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EY1" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Lu  He', 'age': 54, 'title': 'GM &amp; Shareholder Director', 'yearBorn': 1971, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sheng  Wang', 'age': 44, 'title': 'Chief Accountant', 'yearBorn': 1981, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jia Xin  Wu', 'age': 50, 'title': 'General Counsel', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shuang  Liu', 'age': 56, 'title': 'Board Secretary', 'yearBorn': 1969, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Hui', 'age': 52, 'title': 'Deputy General Manager', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zeng Wei  Fan', 'age': 60, 'title': 'Deputy General Manager', 'yearBorn': 1965, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4344,34 +4344,34 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>5.46</v>
+        <v>5.11</v>
       </c>
       <c r="U2" t="n">
-        <v>5.85</v>
+        <v>5.33</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="W2" t="n">
-        <v>5.53</v>
+        <v>5.22</v>
       </c>
       <c r="X2" t="n">
-        <v>5.46</v>
+        <v>5.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.85</v>
+        <v>5.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.53</v>
+        <v>5.22</v>
       </c>
       <c r="AB2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AD2" t="n">
         <v>1780963200</v>
@@ -4380,43 +4380,43 @@
         <v>1.14</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.73</v>
+        <v>0.768</v>
       </c>
       <c r="AG2" t="n">
-        <v>110.4</v>
+        <v>103</v>
       </c>
       <c r="AH2" t="n">
-        <v>36.8</v>
+        <v>34.333332</v>
       </c>
       <c r="AI2" t="n">
-        <v>84191654</v>
+        <v>50044201</v>
       </c>
       <c r="AJ2" t="n">
-        <v>84191654</v>
+        <v>50044201</v>
       </c>
       <c r="AK2" t="n">
-        <v>73107555</v>
+        <v>66219501</v>
       </c>
       <c r="AL2" t="n">
-        <v>58530854</v>
+        <v>54080250</v>
       </c>
       <c r="AM2" t="n">
-        <v>58530854</v>
+        <v>54080250</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.51</v>
+        <v>5.13</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.52</v>
+        <v>5.14</v>
       </c>
       <c r="AP2" t="n">
-        <v>20022534144</v>
+        <v>18680444928</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19804897617</v>
+        <v>18752989136</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.98</v>
+        <v>5.07</v>
       </c>
       <c r="AS2" t="n">
         <v>8.369999999999999</v>
@@ -4428,19 +4428,19 @@
         <v>1.846153</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.5558167</v>
+        <v>1.4515319</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.5626</v>
+        <v>6.3208</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.3809</v>
+        <v>6.35665</v>
       </c>
       <c r="AY2" t="n">
         <v>0.057</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.010439561</v>
+        <v>0.011154599</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -4451,22 +4451,22 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>84172242944</v>
+        <v>82830147584</v>
       </c>
       <c r="BD2" t="n">
         <v>0.01289</v>
       </c>
       <c r="BE2" t="n">
-        <v>2010958835</v>
+        <v>2045417906</v>
       </c>
       <c r="BF2" t="n">
         <v>3627270626</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.41217998</v>
+        <v>0.4028</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.08251</v>
+        <v>0.08248</v>
       </c>
       <c r="BI2" t="n">
         <v>3627270626</v>
@@ -4475,7 +4475,7 @@
         <v>4.845</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.139319</v>
+        <v>1.0629516</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4507,16 +4507,16 @@
         <v>1153872000</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.54</v>
+        <v>6.436</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.05</v>
+        <v>12.842</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.08548712999999999</v>
+        <v>-0.0058365464</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BY2" t="n">
         <v>0.016</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>5.52</v>
+        <v>5.15</v>
       </c>
       <c r="CC2" t="n">
         <v>7.13</v>
@@ -4647,152 +4647,152 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>1.0989</v>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DK2" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.059999943</v>
+        <v>1783062267</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>5.2 - 5.53</t>
+          <t>finmb_9735820</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.78277814</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1033003800000</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.03999996</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>5.09 - 5.22</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>73107555</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.5399999599999999</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.10843372</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>4.98 - 8.37</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.3405018</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>8.548712999999999</v>
-      </c>
-      <c r="DV2" t="n">
+      <c r="DZ2" t="n">
+        <v>66219501</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.07999992</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.015779078</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>5.07 - 8.37</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-3.2199998</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.38470727</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.58365464</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1651229940</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EH2" t="n">
         <v>1651492800</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EI2" t="n">
         <v>0.05</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EJ2" t="n">
         <v>0.15</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EK2" t="n">
         <v>0.14</v>
       </c>
-      <c r="EA2" t="n">
-        <v>39.42857</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-1.0426002</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.15886998</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.8608999000000001</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.13491826</v>
-      </c>
-      <c r="EF2" t="n">
+      <c r="EL2" t="n">
+        <v>36.785713</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-1.1707997</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.18522967</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-1.2066498</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.1898248</v>
+      </c>
+      <c r="EQ2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="ER2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>Jilin Electric Power Co.,Ltd.</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>SPIC Green Energy Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
         <is>
           <t>SPIC GREEN ENERGY CO LTD</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>SPIC Green Energy Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1033003800000</v>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1782111897</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>finmb_9735820</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EV2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
         </is>
       </c>
       <c r="EX2" t="b">
